--- a/data/users.xlsx
+++ b/data/users.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Python\project_file_system\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24C0B9BD-8755-471D-9ED8-FD3B3527E85C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14BB24A9-C22C-4125-BB93-2872BB33A75D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15696" yWindow="1404" windowWidth="15924" windowHeight="14664" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11124" yWindow="0" windowWidth="17172" windowHeight="16680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="93">
   <si>
     <t>用户名</t>
   </si>
@@ -34,13 +34,7 @@
     <t>admin</t>
   </si>
   <si>
-    <t>admin20250328</t>
-  </si>
-  <si>
     <t>肖尚平</t>
-  </si>
-  <si>
-    <t>123456</t>
   </si>
   <si>
     <t>boss</t>
@@ -198,6 +192,119 @@
   </si>
   <si>
     <t>周嘉良</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>s3itab</t>
+  </si>
+  <si>
+    <t>i0r5xl</t>
+  </si>
+  <si>
+    <t>awp04r</t>
+  </si>
+  <si>
+    <t>hwzmfe</t>
+  </si>
+  <si>
+    <t>johmi0</t>
+  </si>
+  <si>
+    <t>r1u7yn</t>
+  </si>
+  <si>
+    <t>d5e0j1</t>
+  </si>
+  <si>
+    <t>3c4iqd</t>
+  </si>
+  <si>
+    <t>gd1ute</t>
+  </si>
+  <si>
+    <t>wroueo</t>
+  </si>
+  <si>
+    <t>s8dn3q</t>
+  </si>
+  <si>
+    <t>ue6i1z</t>
+  </si>
+  <si>
+    <t>ckcm10</t>
+  </si>
+  <si>
+    <t>m29mzo</t>
+  </si>
+  <si>
+    <t>pwklwe</t>
+  </si>
+  <si>
+    <t>nugbj0</t>
+  </si>
+  <si>
+    <t>jyl3ot</t>
+  </si>
+  <si>
+    <t>26ynjn</t>
+  </si>
+  <si>
+    <t>rujus4</t>
+  </si>
+  <si>
+    <t>udhhzy</t>
+  </si>
+  <si>
+    <t>mepd7a</t>
+  </si>
+  <si>
+    <t>r5qi4g</t>
+  </si>
+  <si>
+    <t>wasmw7</t>
+  </si>
+  <si>
+    <t>pgb4vf</t>
+  </si>
+  <si>
+    <t>yiyxqs</t>
+  </si>
+  <si>
+    <t>ex7ga3</t>
+  </si>
+  <si>
+    <t>84b82e</t>
+  </si>
+  <si>
+    <t>mpb1im</t>
+  </si>
+  <si>
+    <t>18llni</t>
+  </si>
+  <si>
+    <t>dv2pth</t>
+  </si>
+  <si>
+    <t>yaew8u</t>
+  </si>
+  <si>
+    <t>gdpkwa</t>
+  </si>
+  <si>
+    <t>ldrsvv</t>
+  </si>
+  <si>
+    <t>lig0w0</t>
+  </si>
+  <si>
+    <t>pbte9u</t>
+  </si>
+  <si>
+    <t>lgy20250328!@#$</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>lgy556517</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -262,11 +369,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -573,6 +681,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="15.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -590,8 +699,8 @@
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
-        <v>4</v>
+      <c r="B2" s="2" t="s">
+        <v>91</v>
       </c>
       <c r="C2" t="s">
         <v>3</v>
@@ -599,398 +708,398 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C3" t="s">
         <v>5</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>57</v>
       </c>
       <c r="C4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>58</v>
       </c>
       <c r="C5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>59</v>
       </c>
       <c r="C6" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="C7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>6</v>
+        <v>61</v>
       </c>
       <c r="C8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>6</v>
+        <v>62</v>
       </c>
       <c r="C9" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="C10" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>6</v>
+        <v>64</v>
       </c>
       <c r="C11" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B12" t="s">
-        <v>6</v>
+        <v>65</v>
       </c>
       <c r="C12" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>6</v>
+        <v>66</v>
       </c>
       <c r="C13" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>6</v>
+        <v>92</v>
       </c>
       <c r="C14" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C15" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B16" t="s">
-        <v>6</v>
+        <v>68</v>
       </c>
       <c r="C16" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B17" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
       <c r="C17" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B18" t="s">
-        <v>6</v>
+        <v>70</v>
       </c>
       <c r="C18" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B19" t="s">
-        <v>6</v>
+        <v>71</v>
       </c>
       <c r="C19" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B20" t="s">
-        <v>6</v>
+        <v>72</v>
       </c>
       <c r="C20" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B21" t="s">
-        <v>6</v>
+        <v>73</v>
       </c>
       <c r="C21" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B22" t="s">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="C22" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B23" t="s">
-        <v>6</v>
+        <v>75</v>
       </c>
       <c r="C23" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B24" t="s">
-        <v>6</v>
+        <v>76</v>
       </c>
       <c r="C24" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B25" t="s">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="C25" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B26" t="s">
-        <v>6</v>
+        <v>78</v>
       </c>
       <c r="C26" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B27" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="C27" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B28" t="s">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="C28" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B29" t="s">
-        <v>6</v>
+        <v>81</v>
       </c>
       <c r="C29" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B30" t="s">
-        <v>6</v>
+        <v>82</v>
       </c>
       <c r="C30" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B31" t="s">
-        <v>6</v>
+        <v>83</v>
       </c>
       <c r="C31" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B32" t="s">
-        <v>6</v>
+        <v>84</v>
       </c>
       <c r="C32" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B33" t="s">
-        <v>6</v>
+        <v>85</v>
       </c>
       <c r="C33" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B34" t="s">
-        <v>6</v>
+        <v>86</v>
       </c>
       <c r="C34" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B35" t="s">
-        <v>6</v>
+        <v>87</v>
       </c>
       <c r="C35" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B36" t="s">
-        <v>6</v>
+        <v>88</v>
       </c>
       <c r="C36" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B37" t="s">
-        <v>6</v>
+        <v>89</v>
       </c>
       <c r="C37" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B38" t="s">
-        <v>6</v>
+        <v>90</v>
       </c>
       <c r="C38" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>

--- a/data/users.xlsx
+++ b/data/users.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Python\project_file_system\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\VSCode\python\project_file_system\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14BB24A9-C22C-4125-BB93-2872BB33A75D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA60232A-872C-4FD5-933D-77FB0DA95D28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11124" yWindow="0" windowWidth="17172" windowHeight="16680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="56">
   <si>
     <t>用户名</t>
   </si>
@@ -192,119 +192,6 @@
   </si>
   <si>
     <t>周嘉良</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>s3itab</t>
-  </si>
-  <si>
-    <t>i0r5xl</t>
-  </si>
-  <si>
-    <t>awp04r</t>
-  </si>
-  <si>
-    <t>hwzmfe</t>
-  </si>
-  <si>
-    <t>johmi0</t>
-  </si>
-  <si>
-    <t>r1u7yn</t>
-  </si>
-  <si>
-    <t>d5e0j1</t>
-  </si>
-  <si>
-    <t>3c4iqd</t>
-  </si>
-  <si>
-    <t>gd1ute</t>
-  </si>
-  <si>
-    <t>wroueo</t>
-  </si>
-  <si>
-    <t>s8dn3q</t>
-  </si>
-  <si>
-    <t>ue6i1z</t>
-  </si>
-  <si>
-    <t>ckcm10</t>
-  </si>
-  <si>
-    <t>m29mzo</t>
-  </si>
-  <si>
-    <t>pwklwe</t>
-  </si>
-  <si>
-    <t>nugbj0</t>
-  </si>
-  <si>
-    <t>jyl3ot</t>
-  </si>
-  <si>
-    <t>26ynjn</t>
-  </si>
-  <si>
-    <t>rujus4</t>
-  </si>
-  <si>
-    <t>udhhzy</t>
-  </si>
-  <si>
-    <t>mepd7a</t>
-  </si>
-  <si>
-    <t>r5qi4g</t>
-  </si>
-  <si>
-    <t>wasmw7</t>
-  </si>
-  <si>
-    <t>pgb4vf</t>
-  </si>
-  <si>
-    <t>yiyxqs</t>
-  </si>
-  <si>
-    <t>ex7ga3</t>
-  </si>
-  <si>
-    <t>84b82e</t>
-  </si>
-  <si>
-    <t>mpb1im</t>
-  </si>
-  <si>
-    <t>18llni</t>
-  </si>
-  <si>
-    <t>dv2pth</t>
-  </si>
-  <si>
-    <t>yaew8u</t>
-  </si>
-  <si>
-    <t>gdpkwa</t>
-  </si>
-  <si>
-    <t>ldrsvv</t>
-  </si>
-  <si>
-    <t>lig0w0</t>
-  </si>
-  <si>
-    <t>pbte9u</t>
-  </si>
-  <si>
-    <t>lgy20250328!@#$</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>lgy556517</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -374,7 +261,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -699,8 +588,8 @@
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>91</v>
+      <c r="B2" s="2">
+        <v>123456</v>
       </c>
       <c r="C2" t="s">
         <v>3</v>
@@ -710,8 +599,8 @@
       <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" t="s">
-        <v>56</v>
+      <c r="B3" s="2">
+        <v>123456</v>
       </c>
       <c r="C3" t="s">
         <v>5</v>
@@ -721,8 +610,8 @@
       <c r="A4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" t="s">
-        <v>57</v>
+      <c r="B4" s="2">
+        <v>123456</v>
       </c>
       <c r="C4" t="s">
         <v>5</v>
@@ -732,8 +621,8 @@
       <c r="A5" t="s">
         <v>7</v>
       </c>
-      <c r="B5" t="s">
-        <v>58</v>
+      <c r="B5" s="2">
+        <v>123456</v>
       </c>
       <c r="C5" t="s">
         <v>8</v>
@@ -743,8 +632,8 @@
       <c r="A6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" t="s">
-        <v>59</v>
+      <c r="B6" s="2">
+        <v>123456</v>
       </c>
       <c r="C6" t="s">
         <v>10</v>
@@ -754,8 +643,8 @@
       <c r="A7" t="s">
         <v>11</v>
       </c>
-      <c r="B7" t="s">
-        <v>60</v>
+      <c r="B7" s="2">
+        <v>123456</v>
       </c>
       <c r="C7" t="s">
         <v>10</v>
@@ -765,8 +654,8 @@
       <c r="A8" t="s">
         <v>12</v>
       </c>
-      <c r="B8" t="s">
-        <v>61</v>
+      <c r="B8" s="2">
+        <v>123456</v>
       </c>
       <c r="C8" t="s">
         <v>10</v>
@@ -776,8 +665,8 @@
       <c r="A9" t="s">
         <v>13</v>
       </c>
-      <c r="B9" t="s">
-        <v>62</v>
+      <c r="B9" s="2">
+        <v>123456</v>
       </c>
       <c r="C9" t="s">
         <v>10</v>
@@ -787,8 +676,8 @@
       <c r="A10" t="s">
         <v>14</v>
       </c>
-      <c r="B10" t="s">
-        <v>63</v>
+      <c r="B10" s="2">
+        <v>123456</v>
       </c>
       <c r="C10" t="s">
         <v>10</v>
@@ -798,8 +687,8 @@
       <c r="A11" t="s">
         <v>15</v>
       </c>
-      <c r="B11" t="s">
-        <v>64</v>
+      <c r="B11" s="2">
+        <v>123456</v>
       </c>
       <c r="C11" t="s">
         <v>10</v>
@@ -809,8 +698,8 @@
       <c r="A12" t="s">
         <v>16</v>
       </c>
-      <c r="B12" t="s">
-        <v>65</v>
+      <c r="B12" s="2">
+        <v>123456</v>
       </c>
       <c r="C12" t="s">
         <v>17</v>
@@ -820,8 +709,8 @@
       <c r="A13" t="s">
         <v>18</v>
       </c>
-      <c r="B13" t="s">
-        <v>66</v>
+      <c r="B13" s="2">
+        <v>123456</v>
       </c>
       <c r="C13" t="s">
         <v>19</v>
@@ -831,8 +720,8 @@
       <c r="A14" t="s">
         <v>20</v>
       </c>
-      <c r="B14" t="s">
-        <v>92</v>
+      <c r="B14" s="2">
+        <v>123456</v>
       </c>
       <c r="C14" t="s">
         <v>21</v>
@@ -842,8 +731,8 @@
       <c r="A15" t="s">
         <v>22</v>
       </c>
-      <c r="B15" t="s">
-        <v>67</v>
+      <c r="B15" s="2">
+        <v>123456</v>
       </c>
       <c r="C15" t="s">
         <v>23</v>
@@ -853,8 +742,8 @@
       <c r="A16" t="s">
         <v>24</v>
       </c>
-      <c r="B16" t="s">
-        <v>68</v>
+      <c r="B16" s="2">
+        <v>123456</v>
       </c>
       <c r="C16" t="s">
         <v>25</v>
@@ -864,8 +753,8 @@
       <c r="A17" t="s">
         <v>26</v>
       </c>
-      <c r="B17" t="s">
-        <v>69</v>
+      <c r="B17" s="2">
+        <v>123456</v>
       </c>
       <c r="C17" t="s">
         <v>27</v>
@@ -875,8 +764,8 @@
       <c r="A18" t="s">
         <v>28</v>
       </c>
-      <c r="B18" t="s">
-        <v>70</v>
+      <c r="B18" s="2">
+        <v>123456</v>
       </c>
       <c r="C18" t="s">
         <v>27</v>
@@ -886,8 +775,8 @@
       <c r="A19" t="s">
         <v>29</v>
       </c>
-      <c r="B19" t="s">
-        <v>71</v>
+      <c r="B19" s="2">
+        <v>123456</v>
       </c>
       <c r="C19" t="s">
         <v>30</v>
@@ -897,8 +786,8 @@
       <c r="A20" t="s">
         <v>31</v>
       </c>
-      <c r="B20" t="s">
-        <v>72</v>
+      <c r="B20" s="2">
+        <v>123456</v>
       </c>
       <c r="C20" t="s">
         <v>30</v>
@@ -908,8 +797,8 @@
       <c r="A21" t="s">
         <v>32</v>
       </c>
-      <c r="B21" t="s">
-        <v>73</v>
+      <c r="B21" s="2">
+        <v>123456</v>
       </c>
       <c r="C21" t="s">
         <v>30</v>
@@ -919,8 +808,8 @@
       <c r="A22" t="s">
         <v>33</v>
       </c>
-      <c r="B22" t="s">
-        <v>74</v>
+      <c r="B22" s="2">
+        <v>123456</v>
       </c>
       <c r="C22" t="s">
         <v>34</v>
@@ -930,8 +819,8 @@
       <c r="A23" t="s">
         <v>35</v>
       </c>
-      <c r="B23" t="s">
-        <v>75</v>
+      <c r="B23" s="2">
+        <v>123456</v>
       </c>
       <c r="C23" t="s">
         <v>34</v>
@@ -941,8 +830,8 @@
       <c r="A24" t="s">
         <v>36</v>
       </c>
-      <c r="B24" t="s">
-        <v>76</v>
+      <c r="B24" s="2">
+        <v>123456</v>
       </c>
       <c r="C24" t="s">
         <v>34</v>
@@ -952,8 +841,8 @@
       <c r="A25" t="s">
         <v>37</v>
       </c>
-      <c r="B25" t="s">
-        <v>77</v>
+      <c r="B25" s="2">
+        <v>123456</v>
       </c>
       <c r="C25" t="s">
         <v>34</v>
@@ -963,8 +852,8 @@
       <c r="A26" t="s">
         <v>38</v>
       </c>
-      <c r="B26" t="s">
-        <v>78</v>
+      <c r="B26" s="2">
+        <v>123456</v>
       </c>
       <c r="C26" t="s">
         <v>39</v>
@@ -974,8 +863,8 @@
       <c r="A27" t="s">
         <v>40</v>
       </c>
-      <c r="B27" t="s">
-        <v>79</v>
+      <c r="B27" s="2">
+        <v>123456</v>
       </c>
       <c r="C27" t="s">
         <v>39</v>
@@ -985,8 +874,8 @@
       <c r="A28" t="s">
         <v>41</v>
       </c>
-      <c r="B28" t="s">
-        <v>80</v>
+      <c r="B28" s="2">
+        <v>123456</v>
       </c>
       <c r="C28" t="s">
         <v>39</v>
@@ -996,8 +885,8 @@
       <c r="A29" t="s">
         <v>42</v>
       </c>
-      <c r="B29" t="s">
-        <v>81</v>
+      <c r="B29" s="2">
+        <v>123456</v>
       </c>
       <c r="C29" t="s">
         <v>43</v>
@@ -1007,8 +896,8 @@
       <c r="A30" t="s">
         <v>44</v>
       </c>
-      <c r="B30" t="s">
-        <v>82</v>
+      <c r="B30" s="2">
+        <v>123456</v>
       </c>
       <c r="C30" t="s">
         <v>43</v>
@@ -1018,8 +907,8 @@
       <c r="A31" t="s">
         <v>45</v>
       </c>
-      <c r="B31" t="s">
-        <v>83</v>
+      <c r="B31" s="2">
+        <v>123456</v>
       </c>
       <c r="C31" t="s">
         <v>43</v>
@@ -1029,8 +918,8 @@
       <c r="A32" t="s">
         <v>46</v>
       </c>
-      <c r="B32" t="s">
-        <v>84</v>
+      <c r="B32" s="2">
+        <v>123456</v>
       </c>
       <c r="C32" t="s">
         <v>47</v>
@@ -1040,8 +929,8 @@
       <c r="A33" t="s">
         <v>52</v>
       </c>
-      <c r="B33" t="s">
-        <v>85</v>
+      <c r="B33" s="2">
+        <v>123456</v>
       </c>
       <c r="C33" t="s">
         <v>47</v>
@@ -1051,8 +940,8 @@
       <c r="A34" t="s">
         <v>48</v>
       </c>
-      <c r="B34" t="s">
-        <v>86</v>
+      <c r="B34" s="2">
+        <v>123456</v>
       </c>
       <c r="C34" t="s">
         <v>47</v>
@@ -1062,8 +951,8 @@
       <c r="A35" t="s">
         <v>51</v>
       </c>
-      <c r="B35" t="s">
-        <v>87</v>
+      <c r="B35" s="2">
+        <v>123456</v>
       </c>
       <c r="C35" t="s">
         <v>49</v>
@@ -1073,8 +962,8 @@
       <c r="A36" t="s">
         <v>50</v>
       </c>
-      <c r="B36" t="s">
-        <v>88</v>
+      <c r="B36" s="2">
+        <v>123456</v>
       </c>
       <c r="C36" t="s">
         <v>49</v>
@@ -1084,8 +973,8 @@
       <c r="A37" t="s">
         <v>53</v>
       </c>
-      <c r="B37" t="s">
-        <v>89</v>
+      <c r="B37" s="2">
+        <v>123456</v>
       </c>
       <c r="C37" t="s">
         <v>54</v>
@@ -1095,8 +984,8 @@
       <c r="A38" t="s">
         <v>55</v>
       </c>
-      <c r="B38" t="s">
-        <v>90</v>
+      <c r="B38" s="2">
+        <v>123456</v>
       </c>
       <c r="C38" t="s">
         <v>54</v>

--- a/data/users.xlsx
+++ b/data/users.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\VSCode\python\project_file_system\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Python\project_file_system\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2CB3D3C-8E96-4948-9CDD-A2DE0D95E1A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20D32183-3DF4-4158-ABF8-2235EDE9CEA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="66">
   <si>
     <t>用户名</t>
   </si>
@@ -34,9 +34,6 @@
     <t>admin</t>
   </si>
   <si>
-    <t>123456</t>
-  </si>
-  <si>
     <t>肖尚平</t>
   </si>
   <si>
@@ -70,6 +67,9 @@
     <t>王意</t>
   </si>
   <si>
+    <t>莫汝怡</t>
+  </si>
+  <si>
     <t>严雨晴</t>
   </si>
   <si>
@@ -133,9 +133,6 @@
     <t>庄展村</t>
   </si>
   <si>
-    <t>张晟</t>
-  </si>
-  <si>
     <t>徐志航</t>
   </si>
   <si>
@@ -181,6 +178,12 @@
     <t>兰东东</t>
   </si>
   <si>
+    <t>粟艳</t>
+  </si>
+  <si>
+    <t>赵婷</t>
+  </si>
+  <si>
     <t>周春飞</t>
   </si>
   <si>
@@ -190,12 +193,31 @@
     <t>周嘉良</t>
   </si>
   <si>
-    <t>钟胜华</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>PMC</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <t>生产文员1</t>
+  </si>
+  <si>
+    <t>生产</t>
+  </si>
+  <si>
+    <t>吴小玉</t>
+  </si>
+  <si>
+    <t>测试员1</t>
+  </si>
+  <si>
+    <t>测试员2</t>
+  </si>
+  <si>
+    <t>测试员3</t>
+  </si>
+  <si>
+    <t>王付裕</t>
+  </si>
+  <si>
+    <t>陈得敬</t>
+  </si>
+  <si>
+    <t>杨伟武</t>
   </si>
 </sst>
 </file>
@@ -566,7 +588,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C38"/>
+  <dimension ref="A1:C47"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -584,8 +606,8 @@
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
-        <v>4</v>
+      <c r="B2">
+        <v>123456</v>
       </c>
       <c r="C2" t="s">
         <v>3</v>
@@ -593,164 +615,164 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3">
+        <v>123457</v>
+      </c>
+      <c r="C3" t="s">
         <v>5</v>
-      </c>
-      <c r="B3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" t="s">
-        <v>4</v>
+        <v>6</v>
+      </c>
+      <c r="B4">
+        <v>123458</v>
       </c>
       <c r="C4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5">
+        <v>123459</v>
+      </c>
+      <c r="C5" t="s">
         <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>123460</v>
+      </c>
+      <c r="C6" t="s">
         <v>10</v>
-      </c>
-      <c r="B6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" t="s">
-        <v>4</v>
+        <v>11</v>
+      </c>
+      <c r="B7">
+        <v>123461</v>
       </c>
       <c r="C7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" t="s">
-        <v>4</v>
+        <v>12</v>
+      </c>
+      <c r="B8">
+        <v>123462</v>
       </c>
       <c r="C8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" t="s">
-        <v>4</v>
+        <v>13</v>
+      </c>
+      <c r="B9">
+        <v>123463</v>
       </c>
       <c r="C9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" t="s">
-        <v>4</v>
+        <v>14</v>
+      </c>
+      <c r="B10">
+        <v>123464</v>
       </c>
       <c r="C10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" t="s">
-        <v>4</v>
+        <v>15</v>
+      </c>
+      <c r="B11">
+        <v>123465</v>
       </c>
       <c r="C11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" t="s">
-        <v>4</v>
+        <v>16</v>
+      </c>
+      <c r="B12">
+        <v>123466</v>
       </c>
       <c r="C12" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" t="s">
-        <v>4</v>
+        <v>18</v>
+      </c>
+      <c r="B13">
+        <v>123467</v>
       </c>
       <c r="C13" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" t="s">
-        <v>4</v>
+        <v>20</v>
+      </c>
+      <c r="B14">
+        <v>123468</v>
       </c>
       <c r="C14" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>24</v>
-      </c>
-      <c r="B15" t="s">
-        <v>4</v>
+        <v>22</v>
+      </c>
+      <c r="B15">
+        <v>123469</v>
       </c>
       <c r="C15" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>26</v>
-      </c>
-      <c r="B16" t="s">
-        <v>4</v>
+        <v>24</v>
+      </c>
+      <c r="B16">
+        <v>123470</v>
       </c>
       <c r="C16" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>28</v>
-      </c>
-      <c r="B17" t="s">
-        <v>4</v>
+        <v>26</v>
+      </c>
+      <c r="B17">
+        <v>123471</v>
       </c>
       <c r="C17" t="s">
         <v>27</v>
@@ -758,21 +780,21 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>29</v>
-      </c>
-      <c r="B18" t="s">
-        <v>4</v>
+        <v>28</v>
+      </c>
+      <c r="B18">
+        <v>123472</v>
       </c>
       <c r="C18" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>31</v>
-      </c>
-      <c r="B19" t="s">
-        <v>4</v>
+        <v>29</v>
+      </c>
+      <c r="B19">
+        <v>123473</v>
       </c>
       <c r="C19" t="s">
         <v>30</v>
@@ -780,10 +802,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>32</v>
-      </c>
-      <c r="B20" t="s">
-        <v>4</v>
+        <v>31</v>
+      </c>
+      <c r="B20">
+        <v>123474</v>
       </c>
       <c r="C20" t="s">
         <v>30</v>
@@ -791,21 +813,21 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>33</v>
-      </c>
-      <c r="B21" t="s">
-        <v>4</v>
+        <v>32</v>
+      </c>
+      <c r="B21">
+        <v>123475</v>
       </c>
       <c r="C21" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>35</v>
-      </c>
-      <c r="B22" t="s">
-        <v>4</v>
+        <v>33</v>
+      </c>
+      <c r="B22">
+        <v>123476</v>
       </c>
       <c r="C22" t="s">
         <v>34</v>
@@ -813,10 +835,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>36</v>
-      </c>
-      <c r="B23" t="s">
-        <v>4</v>
+        <v>35</v>
+      </c>
+      <c r="B23">
+        <v>123477</v>
       </c>
       <c r="C23" t="s">
         <v>34</v>
@@ -824,10 +846,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>37</v>
-      </c>
-      <c r="B24" t="s">
-        <v>4</v>
+        <v>36</v>
+      </c>
+      <c r="B24">
+        <v>123478</v>
       </c>
       <c r="C24" t="s">
         <v>34</v>
@@ -835,156 +857,255 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25">
+        <v>123479</v>
+      </c>
+      <c r="C25" t="s">
         <v>38</v>
-      </c>
-      <c r="B25" t="s">
-        <v>4</v>
-      </c>
-      <c r="C25" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>40</v>
-      </c>
-      <c r="B26" t="s">
-        <v>4</v>
+        <v>39</v>
+      </c>
+      <c r="B26">
+        <v>123480</v>
       </c>
       <c r="C26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>41</v>
-      </c>
-      <c r="B27" t="s">
-        <v>4</v>
+        <v>40</v>
+      </c>
+      <c r="B27">
+        <v>123481</v>
       </c>
       <c r="C27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>41</v>
+      </c>
+      <c r="B28">
+        <v>123482</v>
+      </c>
+      <c r="C28" t="s">
         <v>42</v>
-      </c>
-      <c r="B28" t="s">
-        <v>4</v>
-      </c>
-      <c r="C28" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>44</v>
-      </c>
-      <c r="B29" t="s">
-        <v>4</v>
+        <v>43</v>
+      </c>
+      <c r="B29">
+        <v>123483</v>
       </c>
       <c r="C29" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>45</v>
-      </c>
-      <c r="B30" t="s">
-        <v>4</v>
+        <v>44</v>
+      </c>
+      <c r="B30">
+        <v>123484</v>
       </c>
       <c r="C30" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>45</v>
+      </c>
+      <c r="B31">
+        <v>123485</v>
+      </c>
+      <c r="C31" t="s">
         <v>46</v>
-      </c>
-      <c r="B31" t="s">
-        <v>4</v>
-      </c>
-      <c r="C31" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>48</v>
-      </c>
-      <c r="B32" t="s">
-        <v>4</v>
+        <v>47</v>
+      </c>
+      <c r="B32">
+        <v>123486</v>
       </c>
       <c r="C32" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>49</v>
-      </c>
-      <c r="B33" t="s">
-        <v>4</v>
+        <v>48</v>
+      </c>
+      <c r="B33">
+        <v>123487</v>
       </c>
       <c r="C33" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>49</v>
+      </c>
+      <c r="B34">
+        <v>123488</v>
+      </c>
+      <c r="C34" t="s">
         <v>50</v>
-      </c>
-      <c r="B34" t="s">
-        <v>4</v>
-      </c>
-      <c r="C34" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>52</v>
-      </c>
-      <c r="B35" t="s">
-        <v>4</v>
+        <v>51</v>
+      </c>
+      <c r="B35">
+        <v>123489</v>
       </c>
       <c r="C35" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>53</v>
-      </c>
-      <c r="B36" t="s">
-        <v>4</v>
+        <v>52</v>
+      </c>
+      <c r="B36">
+        <v>123490</v>
       </c>
       <c r="C36" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>55</v>
-      </c>
-      <c r="B37" t="s">
-        <v>4</v>
+        <v>53</v>
+      </c>
+      <c r="B37">
+        <v>123491</v>
       </c>
       <c r="C37" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>54</v>
+      </c>
+      <c r="B38">
+        <v>123492</v>
+      </c>
+      <c r="C38" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
         <v>56</v>
       </c>
-      <c r="B38" t="s">
-        <v>4</v>
-      </c>
-      <c r="C38" t="s">
+      <c r="B39">
+        <v>123493</v>
+      </c>
+      <c r="C39" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
         <v>57</v>
+      </c>
+      <c r="B40">
+        <v>123494</v>
+      </c>
+      <c r="C40" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>59</v>
+      </c>
+      <c r="B41">
+        <v>123495</v>
+      </c>
+      <c r="C41" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>60</v>
+      </c>
+      <c r="B42">
+        <v>123496</v>
+      </c>
+      <c r="C42" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>61</v>
+      </c>
+      <c r="B43">
+        <v>123497</v>
+      </c>
+      <c r="C43" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>62</v>
+      </c>
+      <c r="B44">
+        <v>123498</v>
+      </c>
+      <c r="C44" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>63</v>
+      </c>
+      <c r="B45">
+        <v>123499</v>
+      </c>
+      <c r="C45" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>64</v>
+      </c>
+      <c r="B46">
+        <v>123500</v>
+      </c>
+      <c r="C46" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>65</v>
+      </c>
+      <c r="B47">
+        <v>123501</v>
+      </c>
+      <c r="C47" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/data/users.xlsx
+++ b/data/users.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Python\project_file_system\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20D32183-3DF4-4158-ABF8-2235EDE9CEA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF00D513-7D33-4DAC-B78C-078D0449E0C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -618,7 +618,7 @@
         <v>4</v>
       </c>
       <c r="B3">
-        <v>123457</v>
+        <v>123456</v>
       </c>
       <c r="C3" t="s">
         <v>5</v>
@@ -629,7 +629,7 @@
         <v>6</v>
       </c>
       <c r="B4">
-        <v>123458</v>
+        <v>123456</v>
       </c>
       <c r="C4" t="s">
         <v>5</v>
@@ -640,7 +640,7 @@
         <v>7</v>
       </c>
       <c r="B5">
-        <v>123459</v>
+        <v>123456</v>
       </c>
       <c r="C5" t="s">
         <v>8</v>
@@ -651,7 +651,7 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>123460</v>
+        <v>123456</v>
       </c>
       <c r="C6" t="s">
         <v>10</v>
@@ -662,7 +662,7 @@
         <v>11</v>
       </c>
       <c r="B7">
-        <v>123461</v>
+        <v>123456</v>
       </c>
       <c r="C7" t="s">
         <v>10</v>
@@ -673,7 +673,7 @@
         <v>12</v>
       </c>
       <c r="B8">
-        <v>123462</v>
+        <v>123456</v>
       </c>
       <c r="C8" t="s">
         <v>10</v>
@@ -684,7 +684,7 @@
         <v>13</v>
       </c>
       <c r="B9">
-        <v>123463</v>
+        <v>123456</v>
       </c>
       <c r="C9" t="s">
         <v>10</v>
@@ -695,7 +695,7 @@
         <v>14</v>
       </c>
       <c r="B10">
-        <v>123464</v>
+        <v>123456</v>
       </c>
       <c r="C10" t="s">
         <v>10</v>
@@ -706,7 +706,7 @@
         <v>15</v>
       </c>
       <c r="B11">
-        <v>123465</v>
+        <v>123456</v>
       </c>
       <c r="C11" t="s">
         <v>10</v>
@@ -717,7 +717,7 @@
         <v>16</v>
       </c>
       <c r="B12">
-        <v>123466</v>
+        <v>123456</v>
       </c>
       <c r="C12" t="s">
         <v>17</v>
@@ -728,7 +728,7 @@
         <v>18</v>
       </c>
       <c r="B13">
-        <v>123467</v>
+        <v>123456</v>
       </c>
       <c r="C13" t="s">
         <v>19</v>
@@ -739,7 +739,7 @@
         <v>20</v>
       </c>
       <c r="B14">
-        <v>123468</v>
+        <v>123456</v>
       </c>
       <c r="C14" t="s">
         <v>21</v>
@@ -750,7 +750,7 @@
         <v>22</v>
       </c>
       <c r="B15">
-        <v>123469</v>
+        <v>123456</v>
       </c>
       <c r="C15" t="s">
         <v>23</v>
@@ -761,7 +761,7 @@
         <v>24</v>
       </c>
       <c r="B16">
-        <v>123470</v>
+        <v>123456</v>
       </c>
       <c r="C16" t="s">
         <v>25</v>
@@ -772,7 +772,7 @@
         <v>26</v>
       </c>
       <c r="B17">
-        <v>123471</v>
+        <v>123456</v>
       </c>
       <c r="C17" t="s">
         <v>27</v>
@@ -783,7 +783,7 @@
         <v>28</v>
       </c>
       <c r="B18">
-        <v>123472</v>
+        <v>123456</v>
       </c>
       <c r="C18" t="s">
         <v>27</v>
@@ -794,7 +794,7 @@
         <v>29</v>
       </c>
       <c r="B19">
-        <v>123473</v>
+        <v>123456</v>
       </c>
       <c r="C19" t="s">
         <v>30</v>
@@ -805,7 +805,7 @@
         <v>31</v>
       </c>
       <c r="B20">
-        <v>123474</v>
+        <v>123456</v>
       </c>
       <c r="C20" t="s">
         <v>30</v>
@@ -816,7 +816,7 @@
         <v>32</v>
       </c>
       <c r="B21">
-        <v>123475</v>
+        <v>123456</v>
       </c>
       <c r="C21" t="s">
         <v>30</v>
@@ -827,7 +827,7 @@
         <v>33</v>
       </c>
       <c r="B22">
-        <v>123476</v>
+        <v>123456</v>
       </c>
       <c r="C22" t="s">
         <v>34</v>
@@ -838,7 +838,7 @@
         <v>35</v>
       </c>
       <c r="B23">
-        <v>123477</v>
+        <v>123456</v>
       </c>
       <c r="C23" t="s">
         <v>34</v>
@@ -849,7 +849,7 @@
         <v>36</v>
       </c>
       <c r="B24">
-        <v>123478</v>
+        <v>123456</v>
       </c>
       <c r="C24" t="s">
         <v>34</v>
@@ -860,7 +860,7 @@
         <v>37</v>
       </c>
       <c r="B25">
-        <v>123479</v>
+        <v>123456</v>
       </c>
       <c r="C25" t="s">
         <v>38</v>
@@ -871,7 +871,7 @@
         <v>39</v>
       </c>
       <c r="B26">
-        <v>123480</v>
+        <v>123456</v>
       </c>
       <c r="C26" t="s">
         <v>38</v>
@@ -882,7 +882,7 @@
         <v>40</v>
       </c>
       <c r="B27">
-        <v>123481</v>
+        <v>123456</v>
       </c>
       <c r="C27" t="s">
         <v>38</v>
@@ -893,7 +893,7 @@
         <v>41</v>
       </c>
       <c r="B28">
-        <v>123482</v>
+        <v>123456</v>
       </c>
       <c r="C28" t="s">
         <v>42</v>
@@ -904,7 +904,7 @@
         <v>43</v>
       </c>
       <c r="B29">
-        <v>123483</v>
+        <v>123456</v>
       </c>
       <c r="C29" t="s">
         <v>42</v>
@@ -915,7 +915,7 @@
         <v>44</v>
       </c>
       <c r="B30">
-        <v>123484</v>
+        <v>123456</v>
       </c>
       <c r="C30" t="s">
         <v>42</v>
@@ -926,7 +926,7 @@
         <v>45</v>
       </c>
       <c r="B31">
-        <v>123485</v>
+        <v>123456</v>
       </c>
       <c r="C31" t="s">
         <v>46</v>
@@ -937,7 +937,7 @@
         <v>47</v>
       </c>
       <c r="B32">
-        <v>123486</v>
+        <v>123456</v>
       </c>
       <c r="C32" t="s">
         <v>46</v>
@@ -948,7 +948,7 @@
         <v>48</v>
       </c>
       <c r="B33">
-        <v>123487</v>
+        <v>123456</v>
       </c>
       <c r="C33" t="s">
         <v>46</v>
@@ -959,7 +959,7 @@
         <v>49</v>
       </c>
       <c r="B34">
-        <v>123488</v>
+        <v>123456</v>
       </c>
       <c r="C34" t="s">
         <v>50</v>
@@ -970,7 +970,7 @@
         <v>51</v>
       </c>
       <c r="B35">
-        <v>123489</v>
+        <v>123456</v>
       </c>
       <c r="C35" t="s">
         <v>50</v>
@@ -981,7 +981,7 @@
         <v>52</v>
       </c>
       <c r="B36">
-        <v>123490</v>
+        <v>123456</v>
       </c>
       <c r="C36" t="s">
         <v>50</v>
@@ -992,7 +992,7 @@
         <v>53</v>
       </c>
       <c r="B37">
-        <v>123491</v>
+        <v>123456</v>
       </c>
       <c r="C37" t="s">
         <v>50</v>
@@ -1003,7 +1003,7 @@
         <v>54</v>
       </c>
       <c r="B38">
-        <v>123492</v>
+        <v>123456</v>
       </c>
       <c r="C38" t="s">
         <v>55</v>
@@ -1014,7 +1014,7 @@
         <v>56</v>
       </c>
       <c r="B39">
-        <v>123493</v>
+        <v>123456</v>
       </c>
       <c r="C39" t="s">
         <v>55</v>
@@ -1025,7 +1025,7 @@
         <v>57</v>
       </c>
       <c r="B40">
-        <v>123494</v>
+        <v>123456</v>
       </c>
       <c r="C40" t="s">
         <v>58</v>
@@ -1036,7 +1036,7 @@
         <v>59</v>
       </c>
       <c r="B41">
-        <v>123495</v>
+        <v>123456</v>
       </c>
       <c r="C41" t="s">
         <v>58</v>
@@ -1047,7 +1047,7 @@
         <v>60</v>
       </c>
       <c r="B42">
-        <v>123496</v>
+        <v>123456</v>
       </c>
       <c r="C42" t="s">
         <v>58</v>
@@ -1058,7 +1058,7 @@
         <v>61</v>
       </c>
       <c r="B43">
-        <v>123497</v>
+        <v>123456</v>
       </c>
       <c r="C43" t="s">
         <v>58</v>
@@ -1069,7 +1069,7 @@
         <v>62</v>
       </c>
       <c r="B44">
-        <v>123498</v>
+        <v>123456</v>
       </c>
       <c r="C44" t="s">
         <v>58</v>
@@ -1080,7 +1080,7 @@
         <v>63</v>
       </c>
       <c r="B45">
-        <v>123499</v>
+        <v>123456</v>
       </c>
       <c r="C45" t="s">
         <v>34</v>
@@ -1091,7 +1091,7 @@
         <v>64</v>
       </c>
       <c r="B46">
-        <v>123500</v>
+        <v>123456</v>
       </c>
       <c r="C46" t="s">
         <v>34</v>
@@ -1102,7 +1102,7 @@
         <v>65</v>
       </c>
       <c r="B47">
-        <v>123501</v>
+        <v>123456</v>
       </c>
       <c r="C47" t="s">
         <v>34</v>

--- a/data/users.xlsx
+++ b/data/users.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Python\project_file_system\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF00D513-7D33-4DAC-B78C-078D0449E0C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAAB49E5-9A9A-476F-A73F-B1C902B6CACB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="66">
   <si>
     <t>用户名</t>
   </si>
@@ -157,12 +157,6 @@
     <t>程晋成</t>
   </si>
   <si>
-    <t>邓樟荣</t>
-  </si>
-  <si>
-    <t>工程</t>
-  </si>
-  <si>
     <t>杨铁华</t>
   </si>
   <si>
@@ -218,6 +212,14 @@
   </si>
   <si>
     <t>杨伟武</t>
+  </si>
+  <si>
+    <t>NPI工程</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>IE工程</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -588,7 +590,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C47"/>
+  <dimension ref="A1:C46"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -929,29 +931,29 @@
         <v>123456</v>
       </c>
       <c r="C31" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B32">
         <v>123456</v>
       </c>
       <c r="C32" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>47</v>
+      </c>
+      <c r="B33">
+        <v>123456</v>
+      </c>
+      <c r="C33" t="s">
         <v>48</v>
-      </c>
-      <c r="B33">
-        <v>123456</v>
-      </c>
-      <c r="C33" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -962,40 +964,40 @@
         <v>123456</v>
       </c>
       <c r="C34" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B35">
         <v>123456</v>
       </c>
       <c r="C35" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B36">
         <v>123456</v>
       </c>
       <c r="C36" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>52</v>
+      </c>
+      <c r="B37">
+        <v>123456</v>
+      </c>
+      <c r="C37" t="s">
         <v>53</v>
-      </c>
-      <c r="B37">
-        <v>123456</v>
-      </c>
-      <c r="C37" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -1006,18 +1008,18 @@
         <v>123456</v>
       </c>
       <c r="C38" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>55</v>
+      </c>
+      <c r="B39">
+        <v>123456</v>
+      </c>
+      <c r="C39" t="s">
         <v>56</v>
-      </c>
-      <c r="B39">
-        <v>123456</v>
-      </c>
-      <c r="C39" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -1028,56 +1030,56 @@
         <v>123456</v>
       </c>
       <c r="C40" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B41">
         <v>123456</v>
       </c>
       <c r="C41" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B42">
         <v>123456</v>
       </c>
       <c r="C42" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B43">
         <v>123456</v>
       </c>
       <c r="C43" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B44">
         <v>123456</v>
       </c>
       <c r="C44" t="s">
-        <v>58</v>
+        <v>34</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B45">
         <v>123456</v>
@@ -1088,23 +1090,12 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B46">
         <v>123456</v>
       </c>
       <c r="C46" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>65</v>
-      </c>
-      <c r="B47">
-        <v>123456</v>
-      </c>
-      <c r="C47" t="s">
         <v>34</v>
       </c>
     </row>

--- a/data/users.xlsx
+++ b/data/users.xlsx
@@ -8,19 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Python\project_file_system\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAAB49E5-9A9A-476F-A73F-B1C902B6CACB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4B2F959-4BAD-4AC6-8591-3AA446894B52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="67">
   <si>
     <t>用户名</t>
   </si>
@@ -219,6 +232,10 @@
   </si>
   <si>
     <t>IE工程</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>研发样品组长</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -238,6 +255,7 @@
       <b/>
       <sz val="11"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -592,6 +610,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C46"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="17.44140625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -898,7 +919,7 @@
         <v>123456</v>
       </c>
       <c r="C28" t="s">
-        <v>42</v>
+        <v>66</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">

--- a/data/users.xlsx
+++ b/data/users.xlsx
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>销售</t>
+          <t>销售主管</t>
         </is>
       </c>
     </row>
@@ -1230,7 +1230,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>李鹏</t>
+          <t>李朋</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
